--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="50">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_id</t>
   </si>
@@ -22,10 +38,25 @@
     <t>Position</t>
   </si>
   <si>
-    <t>AttrList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
+    <t>AtrList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
+    <t>FeeBase</t>
+  </si>
+  <si>
+    <t>SpeAtrList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeLevel</t>
   </si>
   <si>
     <t>Id</t>
@@ -43,71 +74,122 @@
     <t>1</t>
   </si>
   <si>
-    <t>2,3,4</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
+    <t>3,1003,2003</t>
+  </si>
+  <si>
+    <t>20,2,2</t>
+  </si>
+  <si>
+    <t>0,20,40,60</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>20,1</t>
+    <t>2,1002,2003</t>
+  </si>
+  <si>
+    <t>10,1,1</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>1,2,3,4</t>
-  </si>
-  <si>
-    <t>10,1,1,1</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>10,1</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>1000,5,2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击率</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>致命率</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>1,2,3,4,5</t>
-  </si>
-  <si>
-    <t>10,1,1,1,1</t>
-  </si>
-  <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,10 +204,23 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -597,150 +692,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1060,143 +1162,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFB15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:XFC16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="8.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5833333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="1" customWidth="1"/>
-    <col min="8" max="16380" width="9" style="1"/>
-    <col min="16383" max="16384" width="9" style="3"/>
+    <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.0833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
+    <col min="13" max="16381" width="9" style="1"/>
+    <col min="16384" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="5:6">
+    <row r="1" s="1" customFormat="1" spans="1:12 16382:16383">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="3:6">
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+    <row r="2" s="1" customFormat="1" spans="1:12 16382:16383">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:6">
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="F3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:6">
-      <c r="C4" s="5" t="s">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="G4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:6">
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>7</v>
-      </c>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="XFA6" s="3"/>
-      <c r="XFB6" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="9">
+        <v>2</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="XFB6" s="4"/>
+      <c r="XFC6" s="4"/>
     </row>
-    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA7" s="3"/>
-      <c r="XFB7" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="XFB7" s="4"/>
+      <c r="XFC7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFA8" s="3"/>
-      <c r="XFB8" s="3"/>
+      <c r="F8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="XFB8" s="4"/>
+      <c r="XFC8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="XFA9" s="3"/>
-      <c r="XFB9" s="3"/>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="XFB9" s="4"/>
+      <c r="XFC9" s="4"/>
     </row>
-    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
@@ -1205,108 +1449,221 @@
       <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFA10" s="3"/>
-      <c r="XFB10" s="3"/>
+      <c r="E10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s">
+        <v>35</v>
+      </c>
+      <c r="XFB10" s="4"/>
+      <c r="XFC10" s="4"/>
     </row>
-    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFA11" s="3"/>
-      <c r="XFB11" s="3"/>
+      <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="XFB11" s="4"/>
+      <c r="XFC11" s="4"/>
     </row>
-    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFA12" s="3"/>
-      <c r="XFB12" s="3"/>
+      <c r="F12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" t="s">
+        <v>42</v>
+      </c>
+      <c r="XFB12" s="4"/>
+      <c r="XFC12" s="4"/>
     </row>
-    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFA13" s="3"/>
-      <c r="XFB13" s="3"/>
+      <c r="F13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="XFB13" s="4"/>
+      <c r="XFC13" s="4"/>
     </row>
-    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="XFA14" s="3"/>
-      <c r="XFB14" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="9">
+        <v>1</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+      <c r="XFB14" s="4"/>
+      <c r="XFC14" s="4"/>
     </row>
-    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="XFA15" s="3"/>
-      <c r="XFB15" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="9">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="XFB15" s="4"/>
+      <c r="XFC15" s="4"/>
+    </row>
+    <row r="16" spans="1:12 16382:16383">
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="K16" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2 D2 C3 D3 D4 D5 C4:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -104,70 +104,70 @@
     <t>10,1,1</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>致命率</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>1000,5,2</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
     <t>命中</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>1000,5,2</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
     <t>5,1,1</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
     <t>暴击率</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>致命率</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>致命伤害</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>10</t>
@@ -1390,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>19</v>
@@ -1399,7 +1399,7 @@
         <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="XFB8" s="4"/>
       <c r="XFC8" s="4"/>
@@ -1408,16 +1408,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>17</v>
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>19</v>
@@ -1435,7 +1435,7 @@
         <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="XFB9" s="4"/>
       <c r="XFC9" s="4"/>
@@ -1453,7 +1453,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>17</v>
@@ -1462,16 +1462,16 @@
         <v>1</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="XFB10" s="4"/>
       <c r="XFC10" s="4"/>
@@ -1480,16 +1480,16 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>17</v>
@@ -1498,16 +1498,16 @@
         <v>1</v>
       </c>
       <c r="I11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="XFB11" s="4"/>
       <c r="XFC11" s="4"/>
@@ -1537,7 +1537,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>20</v>
@@ -1570,16 +1570,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="XFB13" s="4"/>
       <c r="XFC13" s="4"/>
@@ -1588,16 +1588,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>17</v>
@@ -1606,16 +1606,16 @@
         <v>1</v>
       </c>
       <c r="I14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="XFB14" s="4"/>
       <c r="XFC14" s="4"/>
@@ -1630,10 +1630,10 @@
         <v>47</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>17</v>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -101,18 +101,21 @@
     <t>2,1002,2003</t>
   </si>
   <si>
+    <t>2,1,1</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>10,1,1</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -134,7 +137,7 @@
     <t>命中</t>
   </si>
   <si>
-    <t>5,1,1</t>
+    <t>1,1,1</t>
   </si>
   <si>
     <t>22</t>
@@ -1180,7 +1183,7 @@
     <col min="16384" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12 16382:16383">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:12 16382:16383">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
@@ -1192,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12 16382:16383">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:12 16382:16383">
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="2"/>
@@ -1381,7 +1384,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>17</v>
@@ -1390,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>19</v>
@@ -1399,7 +1402,7 @@
         <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="XFB8" s="4"/>
       <c r="XFC8" s="4"/>
@@ -1408,16 +1411,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>17</v>
@@ -1426,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>19</v>
@@ -1435,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="XFB9" s="4"/>
       <c r="XFC9" s="4"/>
@@ -1453,7 +1456,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>17</v>
@@ -1462,16 +1465,16 @@
         <v>1</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="XFB10" s="4"/>
       <c r="XFC10" s="4"/>
@@ -1480,16 +1483,16 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>17</v>
@@ -1498,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="XFB11" s="4"/>
       <c r="XFC11" s="4"/>
@@ -1516,16 +1519,16 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>17</v>
@@ -1534,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="XFB12" s="4"/>
       <c r="XFC12" s="4"/>
@@ -1552,16 +1555,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>17</v>
@@ -1570,16 +1573,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="XFB13" s="4"/>
       <c r="XFC13" s="4"/>
@@ -1588,16 +1591,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>17</v>
@@ -1606,16 +1609,16 @@
         <v>1</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="XFB14" s="4"/>
       <c r="XFC14" s="4"/>
@@ -1624,16 +1627,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>17</v>
@@ -1642,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>19</v>
@@ -1651,7 +1654,7 @@
         <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="XFB15" s="4"/>
       <c r="XFC15" s="4"/>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
   <si>
     <t>#</t>
   </si>
@@ -101,9 +101,6 @@
     <t>2,1002,2003</t>
   </si>
   <si>
-    <t>2,1,1</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
   </si>
   <si>
     <t>命中</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
   </si>
   <si>
     <t>22</t>
@@ -1348,7 +1342,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>17</v>
@@ -1357,7 +1351,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>19</v>
@@ -1366,7 +1360,7 @@
         <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="XFB7" s="4"/>
       <c r="XFC7" s="4"/>
@@ -1375,16 +1369,16 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>17</v>
@@ -1393,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>19</v>
@@ -1402,7 +1396,7 @@
         <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="XFB8" s="4"/>
       <c r="XFC8" s="4"/>
@@ -1411,16 +1405,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" t="s">
         <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>17</v>
@@ -1429,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>19</v>
@@ -1438,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="XFB9" s="4"/>
       <c r="XFC9" s="4"/>
@@ -1456,7 +1450,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>17</v>
@@ -1465,16 +1459,16 @@
         <v>1</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="XFB10" s="4"/>
       <c r="XFC10" s="4"/>
@@ -1483,16 +1477,16 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>17</v>
@@ -1501,16 +1495,16 @@
         <v>1</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="XFB11" s="4"/>
       <c r="XFC11" s="4"/>
@@ -1519,16 +1513,16 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>17</v>
@@ -1537,16 +1531,16 @@
         <v>1</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="XFB12" s="4"/>
       <c r="XFC12" s="4"/>
@@ -1555,16 +1549,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>17</v>
@@ -1573,16 +1567,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="XFB13" s="4"/>
       <c r="XFC13" s="4"/>
@@ -1591,16 +1585,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
         <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>17</v>
@@ -1609,16 +1603,16 @@
         <v>1</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="XFB14" s="4"/>
       <c r="XFC14" s="4"/>
@@ -1627,16 +1621,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
         <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>17</v>
@@ -1645,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>19</v>
@@ -1654,7 +1648,7 @@
         <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="XFB15" s="4"/>
       <c r="XFC15" s="4"/>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>RequireLevel</t>
   </si>
   <si>
+    <t>AtrTypeList</t>
+  </si>
+  <si>
     <t>FeeBase</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
   </si>
   <si>
     <t>0,20,40,60</t>
+  </si>
+  <si>
+    <t>2,1,1,1</t>
   </si>
   <si>
     <t>11</t>
@@ -824,7 +830,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -838,6 +843,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1159,7 +1165,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFC16"/>
+  <dimension ref="A1:XFD16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1167,496 +1173,537 @@
     <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.5833333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.0833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.6666666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
-    <col min="13" max="16381" width="9" style="1"/>
-    <col min="16384" max="16384" width="9" style="4"/>
+    <col min="7" max="8" width="19.9166666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.0833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="1" customWidth="1"/>
+    <col min="14" max="16382" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:12 16382:16383">
+    <row r="1" s="1" customFormat="1" spans="1:13 16383:16384">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:12 16382:16383">
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+    <row r="2" s="1" customFormat="1" spans="1:13 16383:16384">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
-      <c r="C3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="8"/>
+      <c r="L3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="7"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="8"/>
+      <c r="L4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16383">
-      <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>11</v>
+      <c r="F5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="8"/>
+      <c r="K5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="7"/>
     </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="9">
+        <v>18</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="8">
         <v>2</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>19</v>
+      <c r="J6" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" t="s">
         <v>21</v>
       </c>
-      <c r="XFB6" s="4"/>
-      <c r="XFC6" s="4"/>
+      <c r="L6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="XFC6" s="9"/>
+      <c r="XFD6" s="9"/>
     </row>
-    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="8">
+        <v>2</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="9">
-        <v>2</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-      <c r="XFB7" s="4"/>
-      <c r="XFC7" s="4"/>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="XFC7" s="9"/>
+      <c r="XFD7" s="9"/>
     </row>
-    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="9">
+        <v>18</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="8">
         <v>1</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>19</v>
+      <c r="J8" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" t="s">
-        <v>29</v>
-      </c>
-      <c r="XFB8" s="4"/>
-      <c r="XFC8" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="XFC8" s="9"/>
+      <c r="XFD8" s="9"/>
     </row>
-    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="9">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="8">
         <v>1</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>19</v>
+      <c r="J9" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="XFB9" s="4"/>
-      <c r="XFC9" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="XFC9" s="9"/>
+      <c r="XFD9" s="9"/>
     </row>
-    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="I10" s="8">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>36</v>
+      <c r="J10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
-      </c>
-      <c r="XFB10" s="4"/>
-      <c r="XFC10" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="XFC10" s="9"/>
+      <c r="XFD10" s="9"/>
     </row>
-    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" t="s">
-        <v>37</v>
-      </c>
-      <c r="XFB11" s="4"/>
-      <c r="XFC11" s="4"/>
+      <c r="L11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="XFC11" s="9"/>
+      <c r="XFD11" s="9"/>
     </row>
-    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="9">
+        <v>18</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="8">
         <v>1</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>36</v>
+      <c r="J12" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="XFB12" s="4"/>
-      <c r="XFC12" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="XFC12" s="9"/>
+      <c r="XFD12" s="9"/>
     </row>
-    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="9">
-        <v>1</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>36</v>
-      </c>
       <c r="K13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" t="s">
-        <v>41</v>
-      </c>
-      <c r="XFB13" s="4"/>
-      <c r="XFC13" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>43</v>
+      </c>
+      <c r="XFC13" s="9"/>
+      <c r="XFD13" s="9"/>
     </row>
-    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="9">
+        <v>18</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="8">
         <v>1</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>36</v>
+      <c r="J14" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" t="s">
-        <v>45</v>
-      </c>
-      <c r="XFB14" s="4"/>
-      <c r="XFC14" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>47</v>
+      </c>
+      <c r="XFC14" s="9"/>
+      <c r="XFD14" s="9"/>
     </row>
-    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16383">
+    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="9">
+        <v>18</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="8">
         <v>1</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>19</v>
+      <c r="J15" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" t="s">
-        <v>48</v>
-      </c>
-      <c r="XFB15" s="4"/>
-      <c r="XFC15" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="XFC15" s="9"/>
+      <c r="XFD15" s="9"/>
     </row>
-    <row r="16" spans="1:12 16382:16383">
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="K16" s="9"/>
+    <row r="16" spans="1:13 16383:16384">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="L16" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="50">
   <si>
     <t>#</t>
   </si>
@@ -80,7 +80,7 @@
     <t>3,1003,2003</t>
   </si>
   <si>
-    <t>20,2,2</t>
+    <t>10,2,2</t>
   </si>
   <si>
     <t>0,20,40,60</t>
@@ -116,22 +116,19 @@
     <t>3</t>
   </si>
   <si>
-    <t>10,1,1</t>
+    <t>5,1,1</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>致命率</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
     <t>1,1001,1001</t>
   </si>
   <si>
-    <t>1000,5,2</t>
+    <t>100,5,2</t>
   </si>
   <si>
     <t>13</t>
@@ -1421,7 +1418,7 @@
         <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="XFC8" s="9"/>
       <c r="XFD8" s="9"/>
@@ -1430,16 +1427,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>34</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>18</v>
@@ -1451,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>21</v>
@@ -1460,7 +1457,7 @@
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="XFC9" s="9"/>
       <c r="XFD9" s="9"/>
@@ -1490,16 +1487,16 @@
         <v>1</v>
       </c>
       <c r="J10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="XFC10" s="9"/>
       <c r="XFD10" s="9"/>
@@ -1508,10 +1505,10 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>25</v>
@@ -1529,16 +1526,16 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="XFC11" s="9"/>
       <c r="XFD11" s="9"/>
@@ -1547,10 +1544,10 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>16</v>
@@ -1568,16 +1565,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="XFC12" s="9"/>
       <c r="XFD12" s="9"/>
@@ -1586,10 +1583,10 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>16</v>
@@ -1607,16 +1604,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="XFC13" s="9"/>
       <c r="XFD13" s="9"/>
@@ -1625,16 +1622,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
         <v>33</v>
-      </c>
-      <c r="F14" t="s">
-        <v>34</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>18</v>
@@ -1646,16 +1643,16 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="XFC14" s="9"/>
       <c r="XFD14" s="9"/>
@@ -1664,16 +1661,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
         <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>18</v>
@@ -1685,16 +1682,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="XFC15" s="9"/>
       <c r="XFD15" s="9"/>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -107,6 +107,9 @@
     <t>2,1002,2003</t>
   </si>
   <si>
+    <t>30,2,2</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
@@ -128,13 +131,16 @@
     <t>1,1001,1001</t>
   </si>
   <si>
-    <t>100,5,2</t>
+    <t>150,5,2</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
     <t>命中</t>
+  </si>
+  <si>
+    <t>15,1,1</t>
   </si>
   <si>
     <t>22</t>
@@ -1179,7 +1185,7 @@
     <col min="14" max="16382" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13 16383:16384">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:13 16383:16384">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
@@ -1192,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:13 16383:16384">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:13 16383:16384">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="2"/>
@@ -1358,7 +1364,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>18</v>
@@ -1370,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>21</v>
@@ -1379,7 +1385,7 @@
         <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="XFC7" s="9"/>
       <c r="XFD7" s="9"/>
@@ -1388,16 +1394,16 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>18</v>
@@ -1409,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>21</v>
@@ -1427,16 +1433,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>18</v>
@@ -1448,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>21</v>
@@ -1457,7 +1463,7 @@
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="XFC9" s="9"/>
       <c r="XFD9" s="9"/>
@@ -1475,7 +1481,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>18</v>
@@ -1487,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="XFC10" s="9"/>
       <c r="XFD10" s="9"/>
@@ -1505,16 +1511,16 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>18</v>
@@ -1526,16 +1532,16 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="XFC11" s="9"/>
       <c r="XFD11" s="9"/>
@@ -1544,16 +1550,16 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>18</v>
@@ -1565,16 +1571,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="XFC12" s="9"/>
       <c r="XFD12" s="9"/>
@@ -1583,16 +1589,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>18</v>
@@ -1604,16 +1610,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="XFC13" s="9"/>
       <c r="XFD13" s="9"/>
@@ -1622,16 +1628,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>18</v>
@@ -1643,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>21</v>
@@ -1652,7 +1658,7 @@
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="XFC14" s="9"/>
       <c r="XFD14" s="9"/>
@@ -1661,16 +1667,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>18</v>
@@ -1682,16 +1688,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="XFC15" s="9"/>
       <c r="XFD15" s="9"/>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -92,27 +92,30 @@
     <t>11</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2,1002,2003</t>
+  </si>
+  <si>
+    <t>30,2,2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2,1002,2003</t>
-  </si>
-  <si>
-    <t>30,2,2</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>闪避</t>
   </si>
   <si>
@@ -122,7 +125,7 @@
     <t>5,1,1</t>
   </si>
   <si>
-    <t>23</t>
+    <t>冷却</t>
   </si>
   <si>
     <t>4</t>
@@ -146,7 +149,7 @@
     <t>22</t>
   </si>
   <si>
-    <t>20</t>
+    <t>25</t>
   </si>
   <si>
     <t>爆伤</t>
@@ -174,9 +177,6 @@
   </si>
   <si>
     <t>暴击率</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>12</t>
@@ -1379,13 +1379,13 @@
         <v>27</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L7" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="XFC7" s="9"/>
       <c r="XFD7" s="9"/>
@@ -1394,16 +1394,16 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>18</v>
@@ -1415,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>21</v>
@@ -1424,7 +1424,7 @@
         <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="XFC8" s="9"/>
       <c r="XFD8" s="9"/>
@@ -1433,16 +1433,16 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>18</v>
@@ -1454,16 +1454,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L9" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="XFC9" s="9"/>
       <c r="XFD9" s="9"/>
@@ -1472,16 +1472,16 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>18</v>
@@ -1493,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="XFC10" s="9"/>
       <c r="XFD10" s="9"/>
@@ -1511,16 +1511,16 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>18</v>
@@ -1532,16 +1532,16 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="XFC11" s="9"/>
       <c r="XFD11" s="9"/>
@@ -1550,16 +1550,16 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>18</v>
@@ -1571,16 +1571,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="XFC12" s="9"/>
       <c r="XFD12" s="9"/>
@@ -1589,16 +1589,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>18</v>
@@ -1610,16 +1610,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="XFC13" s="9"/>
       <c r="XFD13" s="9"/>
@@ -1628,16 +1628,16 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>18</v>
@@ -1649,16 +1649,16 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="XFC14" s="9"/>
       <c r="XFD14" s="9"/>
@@ -1667,16 +1667,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>18</v>
@@ -1691,7 +1691,7 @@
         <v>50</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>22</v>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -146,28 +146,40 @@
     <t>15,1,1</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>爆伤</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
     <t>致命伤害</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
   <si>
     <t>9</t>
@@ -1532,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>40</v>
@@ -1541,7 +1553,7 @@
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="XFC11" s="9"/>
       <c r="XFD11" s="9"/>
@@ -1550,10 +1562,10 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>16</v>
@@ -1571,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>40</v>
@@ -1580,7 +1592,7 @@
         <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="XFC12" s="9"/>
       <c r="XFD12" s="9"/>
@@ -1589,10 +1601,10 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>16</v>
@@ -1610,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>40</v>
@@ -1619,7 +1631,7 @@
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="XFC13" s="9"/>
       <c r="XFD13" s="9"/>
@@ -1628,10 +1640,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>34</v>
@@ -1649,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>28</v>
@@ -1658,7 +1670,7 @@
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="XFC14" s="9"/>
       <c r="XFD14" s="9"/>
@@ -1688,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>21</v>
@@ -1697,7 +1709,7 @@
         <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="XFC15" s="9"/>
       <c r="XFD15" s="9"/>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,12 @@
     <t>Position</t>
   </si>
   <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
+  </si>
+  <si>
     <t>AtrList</t>
   </si>
   <si>
@@ -104,97 +110,112 @@
     <t>2</t>
   </si>
   <si>
+    <t>2,1002,2002</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>100,2,2</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
     <t>2,1002,2003</t>
   </si>
   <si>
-    <t>30,2,2</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5,1,1</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>150,5,2</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>15,1,1</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>致命伤害</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>移速</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
 </sst>
 </file>
@@ -840,7 +861,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -858,7 +879,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1180,346 +1200,386 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
-    <col min="7" max="8" width="19.9166666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.0833333333333" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.6666666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.8333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.5" style="1" customWidth="1"/>
-    <col min="14" max="16382" width="9" style="1"/>
+    <col min="4" max="6" width="8.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="22.25" style="2" customWidth="1"/>
+    <col min="9" max="10" width="19.9166666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.0833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:13 16383:16384">
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="1" t="s">
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:13 16383:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="1" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+      <c r="M3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:13 16383:16384">
+      <c r="M4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>13</v>
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+      <c r="L5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" customFormat="1" customHeight="1" spans="1:15">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="8">
         <v>2</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="XFC6" s="9"/>
-      <c r="XFD6" s="9"/>
-    </row>
-    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+      <c r="N6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" customHeight="1" spans="1:15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="8">
+        <v>2</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" t="s">
-        <v>29</v>
-      </c>
-      <c r="XFC7" s="9"/>
-      <c r="XFD7" s="9"/>
-    </row>
-    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1</v>
+      <c r="H8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="XFC8" s="9"/>
-      <c r="XFD8" s="9"/>
-    </row>
-    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" customHeight="1" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="XFC9" s="9"/>
-      <c r="XFD9" s="9"/>
-    </row>
-    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+      <c r="M9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" customHeight="1" spans="1:15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="M10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="N10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" t="s">
         <v>41</v>
       </c>
-      <c r="XFC10" s="9"/>
-      <c r="XFD10" s="9"/>
-    </row>
-    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+    </row>
+    <row r="11" customFormat="1" customHeight="1" spans="1:15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
@@ -1528,37 +1588,41 @@
       <c r="D11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1</v>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="M11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="N11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" t="s">
         <v>44</v>
       </c>
-      <c r="XFC11" s="9"/>
-      <c r="XFD11" s="9"/>
-    </row>
-    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+    </row>
+    <row r="12" customFormat="1" customHeight="1" spans="1:15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
@@ -1567,37 +1631,41 @@
       <c r="D12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1</v>
+      <c r="H12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="M12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="N12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" t="s">
         <v>47</v>
       </c>
-      <c r="XFC12" s="9"/>
-      <c r="XFD12" s="9"/>
-    </row>
-    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+    </row>
+    <row r="13" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
@@ -1606,37 +1674,41 @@
       <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="11" t="s">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="8">
-        <v>1</v>
+      <c r="H13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="M13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="N13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" t="s">
         <v>50</v>
       </c>
-      <c r="XFC13" s="9"/>
-      <c r="XFD13" s="9"/>
-    </row>
-    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+    </row>
+    <row r="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
@@ -1645,84 +1717,565 @@
       <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="8">
-        <v>1</v>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="J14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="M14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
         <v>53</v>
       </c>
-      <c r="XFC14" s="9"/>
-      <c r="XFD14" s="9"/>
-    </row>
-    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:13 16383:16384">
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="1:15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D15" t="s">
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>31</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="K17" s="8">
+        <v>2</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>31</v>
+      </c>
+      <c r="F18">
+        <v>60</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="8">
+        <v>2</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19">
+        <v>31</v>
+      </c>
+      <c r="F19">
+        <v>60</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
+      <c r="E20">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21">
+        <v>31</v>
+      </c>
+      <c r="F21">
+        <v>60</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22">
+        <v>31</v>
+      </c>
+      <c r="F22">
+        <v>60</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="8">
+        <v>1</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23">
+        <v>31</v>
+      </c>
+      <c r="F23">
+        <v>60</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="8">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10" t="s">
+      <c r="H23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24">
+        <v>31</v>
+      </c>
+      <c r="F24">
+        <v>60</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="8">
+        <v>1</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>60</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="8">
+        <v>1</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>31</v>
+      </c>
+      <c r="F26">
+        <v>60</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1</v>
+      </c>
+      <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="M26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" t="s">
         <v>55</v>
       </c>
-      <c r="XFC15" s="9"/>
-      <c r="XFD15" s="9"/>
-    </row>
-    <row r="16" spans="1:13 16383:16384">
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="L16" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -116,79 +116,79 @@
     <t>14</t>
   </si>
   <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>100,2,2</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5,1,1</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>100,2,2</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>致命伤害</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击率</t>
+    <t>抗暴</t>
   </si>
   <si>
     <t>12</t>
@@ -198,9 +198,6 @@
   </si>
   <si>
     <t>2,1002,2003</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>16</t>
@@ -1441,23 +1438,23 @@
         <v>28</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1469,7 +1466,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -1490,17 +1487,17 @@
         <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1509,10 +1506,10 @@
         <v>30</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
         <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>20</v>
@@ -1524,26 +1521,26 @@
         <v>1</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1555,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>20</v>
@@ -1598,7 +1595,7 @@
         <v>27</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>20</v>
@@ -1641,7 +1638,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>20</v>
@@ -1656,7 +1653,7 @@
         <v>46</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>24</v>
@@ -1684,7 +1681,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>20</v>
@@ -1699,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>24</v>
@@ -1724,10 +1721,10 @@
         <v>30</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
         <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>36</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>20</v>
@@ -1742,7 +1739,7 @@
         <v>52</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>24</v>
@@ -1767,10 +1764,10 @@
         <v>30</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
         <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>36</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>20</v>
@@ -1888,13 +1885,13 @@
         <v>28</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N18" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:15">
@@ -1905,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -1920,7 +1917,7 @@
         <v>18</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>20</v>
@@ -1941,7 +1938,7 @@
         <v>24</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:15">
@@ -1955,7 +1952,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>31</v>
@@ -1964,10 +1961,10 @@
         <v>60</v>
       </c>
       <c r="G20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" t="s">
         <v>35</v>
-      </c>
-      <c r="H20" t="s">
-        <v>36</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>20</v>
@@ -1979,16 +1976,16 @@
         <v>1</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:15">
@@ -1999,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>31</v>
@@ -2014,7 +2011,7 @@
         <v>56</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>20</v>
@@ -2029,7 +2026,7 @@
         <v>39</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>24</v>
@@ -2046,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
         <v>42</v>
@@ -2061,7 +2058,7 @@
         <v>56</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>20</v>
@@ -2076,7 +2073,7 @@
         <v>43</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N22" s="10" t="s">
         <v>24</v>
@@ -2093,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
@@ -2108,7 +2105,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>20</v>
@@ -2123,7 +2120,7 @@
         <v>46</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N23" s="10" t="s">
         <v>24</v>
@@ -2140,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
@@ -2155,7 +2152,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>20</v>
@@ -2170,7 +2167,7 @@
         <v>49</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N24" s="10" t="s">
         <v>24</v>
@@ -2187,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>51</v>
@@ -2199,10 +2196,10 @@
         <v>60</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="s">
         <v>35</v>
-      </c>
-      <c r="H25" t="s">
-        <v>36</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>20</v>
@@ -2217,7 +2214,7 @@
         <v>52</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N25" s="10" t="s">
         <v>24</v>
@@ -2234,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -2246,10 +2243,10 @@
         <v>60</v>
       </c>
       <c r="G26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" t="s">
         <v>35</v>
-      </c>
-      <c r="H26" t="s">
-        <v>36</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>20</v>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -131,73 +131,76 @@
     <t>4</t>
   </si>
   <si>
+    <t>1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,2,2</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>抗暴</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>2,1002,2003</t>
+  </si>
+  <si>
     <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>100,2,2</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>抗暴</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>2,1002,2003</t>
   </si>
   <si>
     <t>16</t>
@@ -1961,7 +1964,7 @@
         <v>60</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
@@ -2043,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
         <v>42</v>
@@ -2090,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
@@ -2137,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
@@ -2184,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
         <v>51</v>
@@ -2196,7 +2199,7 @@
         <v>60</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="H25" t="s">
         <v>35</v>
@@ -2231,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -2243,7 +2246,7 @@
         <v>60</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="H26" t="s">
         <v>35</v>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -146,6 +146,18 @@
     <t>5</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
@@ -155,16 +167,40 @@
     <t>增伤</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>抗暴</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>30.60</t>
+  </si>
+  <si>
+    <t>2,1002,2003</t>
+  </si>
+  <si>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>21</t>
@@ -173,7 +209,7 @@
     <t>暴击率</t>
   </si>
   <si>
-    <t>8</t>
+    <t>18</t>
   </si>
   <si>
     <t>22</t>
@@ -182,40 +218,7 @@
     <t>爆伤</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>抗暴</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>2,1002,2003</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
 </sst>
 </file>
@@ -1570,23 +1573,23 @@
         <v>39</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1610,26 +1613,26 @@
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1653,26 +1656,26 @@
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1696,26 +1699,26 @@
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1739,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>23</v>
@@ -1748,7 +1751,7 @@
         <v>24</v>
       </c>
       <c r="O14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:15">
@@ -1782,16 +1785,16 @@
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:15">
@@ -1844,7 +1847,7 @@
         <v>23</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O17" t="s">
         <v>25</v>
@@ -1858,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1870,7 +1873,7 @@
         <v>60</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>19</v>
@@ -1891,7 +1894,7 @@
         <v>38</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O18" t="s">
         <v>29</v>
@@ -1938,7 +1941,7 @@
         <v>23</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O19" t="s">
         <v>32</v>
@@ -1964,7 +1967,7 @@
         <v>60</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
@@ -1985,7 +1988,7 @@
         <v>38</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O20" t="s">
         <v>37</v>
@@ -1999,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
@@ -2011,7 +2014,7 @@
         <v>60</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>31</v>
@@ -2026,16 +2029,16 @@
         <v>1</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:15">
@@ -2046,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22">
         <v>31</v>
@@ -2058,7 +2061,7 @@
         <v>60</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>31</v>
@@ -2073,16 +2076,16 @@
         <v>1</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:15">
@@ -2093,10 +2096,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E23">
         <v>31</v>
@@ -2120,16 +2123,16 @@
         <v>1</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>38</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O23" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:15">
@@ -2143,7 +2146,7 @@
         <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E24">
         <v>31</v>
@@ -2167,16 +2170,16 @@
         <v>1</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O24" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:15">
@@ -2187,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E25">
         <v>31</v>
@@ -2199,7 +2202,7 @@
         <v>60</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H25" t="s">
         <v>35</v>
@@ -2214,16 +2217,16 @@
         <v>1</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>38</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:15">
@@ -2234,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -2246,7 +2249,7 @@
         <v>60</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
         <v>35</v>
@@ -2261,16 +2264,16 @@
         <v>1</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>23</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -95,130 +100,166 @@
     <t>2,1,1,1</t>
   </si>
   <si>
+    <t>11,10001</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>30,60</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2,1002,2002</t>
+  </si>
+  <si>
+    <t>14,14</t>
+  </si>
+  <si>
+    <t>10,15</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>10,10002</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,2,2</t>
+  </si>
+  <si>
+    <t>13,13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>28,28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>27,27</t>
+  </si>
+  <si>
+    <t>15,20</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>25,25</t>
+  </si>
+  <si>
+    <t>抗暴</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>12,12</t>
+  </si>
+  <si>
+    <t>20,30</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2,1002,2002</t>
+    <t>30.60</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2,1002,2003</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5,1,1</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1,1001,2001</t>
-  </si>
-  <si>
-    <t>100,2,2</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>1,1001,1001</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>抗暴</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>30.60</t>
-  </si>
-  <si>
-    <t>2,1002,2003</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
 </sst>
 </file>
@@ -1444,23 +1485,23 @@
         <v>28</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1472,7 +1513,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -1484,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>23</v>
@@ -1493,17 +1534,17 @@
         <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1512,10 +1553,10 @@
         <v>30</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>20</v>
@@ -1527,26 +1568,26 @@
         <v>1</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1558,7 +1599,7 @@
         <v>27</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>20</v>
@@ -1570,26 +1611,26 @@
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1601,7 +1642,7 @@
         <v>27</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>20</v>
@@ -1613,26 +1654,26 @@
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1644,7 +1685,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>20</v>
@@ -1656,26 +1697,26 @@
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1687,7 +1728,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>20</v>
@@ -1699,26 +1740,26 @@
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1727,10 +1768,10 @@
         <v>30</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>20</v>
@@ -1742,26 +1783,26 @@
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1770,10 +1811,10 @@
         <v>30</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>20</v>
@@ -1785,16 +1826,16 @@
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:15">
@@ -1814,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -1841,13 +1882,13 @@
         <v>2</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O17" t="s">
         <v>25</v>
@@ -1861,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1873,7 +1914,7 @@
         <v>60</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>19</v>
@@ -1888,16 +1929,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:15">
@@ -1908,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -1923,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>20</v>
@@ -1935,16 +1976,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:15">
@@ -1955,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>31</v>
@@ -1967,10 +2008,10 @@
         <v>60</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>20</v>
@@ -1982,16 +2023,16 @@
         <v>1</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:15">
@@ -2002,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>31</v>
@@ -2014,10 +2055,10 @@
         <v>60</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>20</v>
@@ -2029,16 +2070,16 @@
         <v>1</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:15">
@@ -2049,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E22">
         <v>31</v>
@@ -2061,10 +2102,10 @@
         <v>60</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>20</v>
@@ -2076,16 +2117,16 @@
         <v>1</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:15">
@@ -2096,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23">
         <v>31</v>
@@ -2111,7 +2152,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>20</v>
@@ -2123,16 +2164,16 @@
         <v>1</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:15">
@@ -2143,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E24">
         <v>31</v>
@@ -2158,7 +2199,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>20</v>
@@ -2170,16 +2211,16 @@
         <v>1</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O24" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:15">
@@ -2190,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>31</v>
@@ -2202,10 +2243,10 @@
         <v>60</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>20</v>
@@ -2217,16 +2258,16 @@
         <v>1</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:15">
@@ -2237,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E26">
         <v>31</v>
@@ -2249,10 +2290,10 @@
         <v>60</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>20</v>
@@ -2264,16 +2305,16 @@
         <v>1</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipStrengthConfig.xlsx
+++ b/Excel/EquipStrengthConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -100,10 +100,10 @@
     <t>2,1,1,1</t>
   </si>
   <si>
-    <t>11,10001</t>
-  </si>
-  <si>
-    <t>10,5</t>
+    <t>11,10003</t>
+  </si>
+  <si>
+    <t>10,10</t>
   </si>
   <si>
     <t>30,60</t>
@@ -118,54 +118,57 @@
     <t>2,1002,2002</t>
   </si>
   <si>
-    <t>14,14</t>
+    <t>14,10002</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>10,10001</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,2,2</t>
+  </si>
+  <si>
+    <t>13,13</t>
   </si>
   <si>
     <t>10,15</t>
   </si>
   <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5,1,1</t>
-  </si>
-  <si>
-    <t>10,10002</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1,1001,2001</t>
-  </si>
-  <si>
-    <t>100,2,2</t>
-  </si>
-  <si>
-    <t>13,13</t>
-  </si>
-  <si>
     <t>命中</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>28,14</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>28,28</t>
   </si>
   <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -200,66 +203,6 @@
   </si>
   <si>
     <t>移速</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>30.60</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2,1002,2003</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1,1001,1001</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
 </sst>
 </file>
@@ -1485,23 +1428,23 @@
         <v>28</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1513,7 +1456,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -1525,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>23</v>
@@ -1534,17 +1477,17 @@
         <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1553,10 +1496,10 @@
         <v>30</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>20</v>
@@ -1568,10 +1511,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>24</v>
@@ -1599,7 +1542,7 @@
         <v>27</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>20</v>
@@ -1614,7 +1557,7 @@
         <v>41</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>24</v>
@@ -1642,7 +1585,7 @@
         <v>27</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>20</v>
@@ -1654,10 +1597,10 @@
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>24</v>
@@ -1670,10 +1613,10 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1685,7 +1628,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>20</v>
@@ -1697,26 +1640,26 @@
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1728,7 +1671,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>20</v>
@@ -1740,26 +1683,26 @@
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1768,10 +1711,10 @@
         <v>30</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
         <v>36</v>
-      </c>
-      <c r="H14" t="s">
-        <v>37</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>20</v>
@@ -1783,26 +1726,26 @@
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1811,10 +1754,10 @@
         <v>30</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
         <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>37</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>20</v>
@@ -1826,16 +1769,16 @@
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:15">
@@ -1847,475 +1790,155 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" customHeight="1" spans="1:15">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17">
-        <v>31</v>
-      </c>
-      <c r="F17">
-        <v>60</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="8">
-        <v>2</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:15">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>60</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="8">
-        <v>2</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:15">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19">
-        <v>31</v>
-      </c>
-      <c r="F19">
-        <v>60</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:15">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20">
-        <v>31</v>
-      </c>
-      <c r="F20">
-        <v>60</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="8">
-        <v>1</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:15">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21">
-        <v>31</v>
-      </c>
-      <c r="F21">
-        <v>60</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="8">
-        <v>1</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:15">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22">
-        <v>31</v>
-      </c>
-      <c r="F22">
-        <v>60</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="8">
-        <v>1</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:15">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23">
-        <v>31</v>
-      </c>
-      <c r="F23">
-        <v>60</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="8">
-        <v>1</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:15">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24">
-        <v>31</v>
-      </c>
-      <c r="F24">
-        <v>60</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="8">
-        <v>1</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:15">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25">
-        <v>31</v>
-      </c>
-      <c r="F25">
-        <v>60</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="8">
-        <v>1</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:15">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26">
-        <v>31</v>
-      </c>
-      <c r="F26">
-        <v>60</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="8">
-        <v>1</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O26" t="s">
-        <v>55</v>
-      </c>
+    <row r="17" customHeight="1" spans="3:15">
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:15">
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:15">
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:15">
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:15">
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:15">
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:15">
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:15">
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:15">
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:15">
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26"/>
     </row>
   </sheetData>
   <dataValidations count="1">
